--- a/nr-fix/ig/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/nr-fix/ig/StructureDefinition-mesures-observation-glucose.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:05:32+00:00</t>
+    <t>2026-03-31T09:17:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
